--- a/output/supplementary/Table1_cohort_summary.xlsx
+++ b/output/supplementary/Table1_cohort_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[22.3%-27.4%]</t>
+          <t>[22.2%-27.4%]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[18.5%-23.4%]</t>
+          <t>[18.5%-23.3%]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -644,17 +644,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[20.9%-26.0%]</t>
+          <t>[20.9%-25.9%]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[24.8%-30.1%]</t>
+          <t>[24.7%-30.0%]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[8.9%-12.6%]</t>
+          <t>[9.0%-12.7%]</t>
         </is>
       </c>
     </row>
@@ -695,264 +695,174 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[15.8%-75.0%]</t>
+          <t>[13.7%-69.4%]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[2.6%-51.3%]</t>
+          <t>[2.2%-47.1%]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[2.6%-51.3%]</t>
+          <t>[2.2%-47.1%]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[8.2%-64.1%]</t>
+          <t>[7.1%-59.1%]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[2.6%-51.3%]</t>
+          <t>[2.2%-47.1%]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[8.2%-64.1%]</t>
+          <t>[7.1%-59.1%]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[8.2%-64.1%]</t>
+          <t>[7.1%-59.1%]</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[25.0%-84.2%]</t>
+          <t>[21.5%-78.5%]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>PMA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[7.1%-59.1%]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[7.1%-59.1%]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>[0.0%-56.2%]</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[0.0%-32.4%]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>[7.1%-59.1%]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>[7.1%-59.1%]</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[0.0%-56.2%]</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>[0.0%-32.4%]</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[0.0%-56.2%]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>[0.0%-56.2%]</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>[0.0%-56.2%]</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>[0.0%-56.2%]</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[0.0%-56.2%]</t>
+          <t>[0.0%-32.4%]</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
-        <is>
-          <t>[6.1%-79.2%]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PMA</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[7.1%-59.1%]</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[7.1%-59.1%]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[0.0%-32.4%]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>[7.1%-59.1%]</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>[7.1%-59.1%]</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>[0.0%-32.4%]</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>[0.0%-32.4%]</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
         <is>
           <t>[21.5%-78.5%]</t>
         </is>
